--- a/財務管理系統.xlsx
+++ b/財務管理系統.xlsx
@@ -1971,7 +1971,7 @@
       </c>
       <c r="D22" s="132" t="inlineStr">
         <is>
-          <t>平準型，保額1044萬(25年)，保費83萬/41.5萬</t>
+          <t>平準型，保額1044萬(25年)；總保費82萬9249元，與弟弟共同分攤，本人負擔41萬4625元</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
         <v>10440000</v>
       </c>
       <c r="E15" s="147" t="n">
-        <v>830000</v>
+        <v>414625</v>
       </c>
       <c r="F15" s="146" t="n">
         <v>25</v>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="M15" s="132" t="inlineStr">
         <is>
-          <t>平準型，保障25年，保費83萬/41.5萬；起始日同東區房貸</t>
+          <t>平準型，保障25年；總保費82萬9249元與弟弟共同分攤，本人負擔41萬4625元；起始日同東區房貸</t>
         </is>
       </c>
     </row>
